--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/01_MyClaimsPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/01_MyClaimsPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD559C7-859B-4A11-84BF-899BD8252EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F53391E-3E27-41AA-8A7C-D149F796054B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/01_MyClaimsPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/01_MyClaimsPageTest.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/01_MyClaimsPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/01_MyClaimsPageTest.xlsx
@@ -16,6 +16,7 @@
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/01_MyClaimsPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/01_MyClaimsPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F53391E-3E27-41AA-8A7C-D149F796054B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54770A87-220E-4D1D-8D22-C252AEF032D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -919,7 +918,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1102,6 +1101,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1306,7 +1311,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1320,6 +1325,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1829,10 +1835,10 @@
       <c r="E5" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="9" t="s">
         <v>64</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -1858,10 +1864,10 @@
       <c r="E6" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="9" t="s">
         <v>66</v>
       </c>
       <c r="H6" s="1" t="s">
@@ -1887,10 +1893,10 @@
       <c r="E7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="9" t="s">
         <v>66</v>
       </c>
       <c r="H7" s="1" t="s">
@@ -1939,10 +1945,10 @@
       <c r="E9" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="9" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="1" t="s">
@@ -1968,10 +1974,10 @@
       <c r="E10" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="9" t="s">
         <v>66</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -1997,10 +2003,10 @@
       <c r="E11" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="9" t="s">
         <v>66</v>
       </c>
       <c r="H11" s="1"/>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/01_MyClaimsPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/01_MyClaimsPageTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54770A87-220E-4D1D-8D22-C252AEF032D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399A1D07-FAA6-493C-9900-6397B74C5601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/01_MyClaimsPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/01_MyClaimsPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399A1D07-FAA6-493C-9900-6397B74C5601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730CFFDF-1105-4520-90ED-19A1BCF85F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -764,6 +764,27 @@
   </si>
   <si>
     <t>2602000005</t>
+  </si>
+  <si>
+    <t>EXPECTED_KEY</t>
+  </si>
+  <si>
+    <t>MYCLIAMS_CLAIMID</t>
+  </si>
+  <si>
+    <t>MYCLIAMS_DEALERNAME</t>
+  </si>
+  <si>
+    <t>MYCLIAMS_PRODUCTDESC</t>
+  </si>
+  <si>
+    <t>MYCLIAMS_INVNO</t>
+  </si>
+  <si>
+    <t>MYCLIAMS_CLAIMQTY</t>
+  </si>
+  <si>
+    <t>MYCLIAMS_CLAIMPOINTS</t>
   </si>
 </sst>
 </file>
@@ -918,7 +939,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1107,6 +1128,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1311,7 +1338,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1326,6 +1353,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1702,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
@@ -1710,12 +1742,13 @@
     <col min="3" max="3" width="24.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="74.36328125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="30.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20.81640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="2"/>
+    <col min="8" max="8" width="30.26953125" style="12" customWidth="1"/>
+    <col min="9" max="9" width="20.81640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
@@ -1738,13 +1771,16 @@
         <v>47</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>75</v>
       </c>
@@ -1762,14 +1798,15 @@
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>75</v>
       </c>
@@ -1787,14 +1824,15 @@
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="10"/>
+      <c r="I3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>75</v>
       </c>
@@ -1812,14 +1850,15 @@
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="10"/>
+      <c r="I4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>75</v>
       </c>
@@ -1841,14 +1880,15 @@
       <c r="G5" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="11"/>
+      <c r="I5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>75</v>
       </c>
@@ -1870,14 +1910,15 @@
       <c r="G6" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="11"/>
+      <c r="I6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -1899,14 +1940,15 @@
       <c r="G7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="11"/>
+      <c r="I7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>75</v>
       </c>
@@ -1922,14 +1964,14 @@
       <c r="E8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>75</v>
       </c>
@@ -1951,14 +1993,15 @@
       <c r="G9" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="11"/>
+      <c r="I9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>75</v>
       </c>
@@ -1980,14 +2023,15 @@
       <c r="G10" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="11"/>
+      <c r="I10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="145" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="145" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>75</v>
       </c>
@@ -2009,12 +2053,15 @@
       <c r="G11" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1" t="s">
+      <c r="H11" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>75</v>
       </c>
@@ -2032,12 +2079,15 @@
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1" t="s">
+      <c r="H12" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>75</v>
       </c>
@@ -2055,12 +2105,15 @@
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1" t="s">
+      <c r="H13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>75</v>
       </c>
@@ -2078,12 +2131,15 @@
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1" t="s">
+      <c r="H14" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>75</v>
       </c>
@@ -2101,12 +2157,15 @@
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1" t="s">
+      <c r="H15" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>75</v>
       </c>
@@ -2124,12 +2183,15 @@
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1" t="s">
+      <c r="H16" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>75</v>
       </c>
@@ -2147,14 +2209,15 @@
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="11"/>
+      <c r="I17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>75</v>
       </c>
@@ -2172,10 +2235,11 @@
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="11"/>
+      <c r="I18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>5</v>
       </c>
     </row>
